--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,6 +1366,120 @@
       <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120093072</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137271436</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56881</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset O, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468261</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546845</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271436</t>
         </is>
       </c>
     </row>
@@ -1377,6 +1491,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>137271436</v>
       </c>
       <c r="B8" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>137271436</v>
       </c>
       <c r="B8" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -1374,7 +1374,7 @@
         <v>137271436</v>
       </c>
       <c r="B8" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
